--- a/data/5.4.3_EL/graphen_bereinigt.xlsx
+++ b/data/5.4.3_EL/graphen_bereinigt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/svetlanayakutina/Documents/GitHub/Digitalisat2Graph/data/5.4.3_EL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AB94C3-05EF-C94C-8090-16319C4D46AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBB142B-E9B5-2C42-81DE-6880EBB88BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21680" yWindow="500" windowWidth="22500" windowHeight="23160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="44800" windowHeight="25200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
